--- a/supplementary-materials/tables/Table_S17.xlsx
+++ b/supplementary-materials/tables/Table_S17.xlsx
@@ -289,7 +289,7 @@
     <t>spOccupancy tPGOcc</t>
   </si>
   <si>
-    <t>Standardised coefficients: Normal(0, 2.25); detection-site variance: inverse-Gamma(2, 1)</t>
+    <t/>
   </si>
   <si>
     <t>Formal: 4 chains × 50,000 iterations; 20,000 burn-in; thin 20. Repair CV: 4 × 30,000; 10,000 burn-in; thin 20</t>
@@ -310,7 +310,7 @@
     <t>Potential-host and Koel occupancy</t>
   </si>
   <si>
-    <t>Occurrence and detection coefficients: Normal(0, 2.25); detection variance: inverse-Gamma(2, 1); occurrence variance also inverse-Gamma(2, 1) when present</t>
+    <t/>
   </si>
   <si>
     <t>Full-data Koel, corvid and laughingthrush fits: 4 × 30,000 iterations; 10,000 burn-in; thin 20. Retained sturnid host refit: 4 × 60,000 iterations; 20,000 burn-in; thin 20.</t>
@@ -427,7 +427,7 @@
     <t>Hourly priors as above; equal-scale host effect inherited from the daily HEQZ branch</t>
   </si>
   <si>
-    <t>Three sampled-surface Koel fits, each 4 chains with 1,000 warm-up + 1,000 sampling iterations</t>
+    <t/>
   </si>
   <si>
     <t>475027 + sampled-surface offset; deterministic posterior-row schedule</t>
@@ -454,7 +454,7 @@
     <t>Stage-specific deterministic seeds stored in registries</t>
   </si>
   <si>
-    <t>Fixed 13,714-cell grid; 52 weeks; 300 posterior draws for exposure/urban summaries; AOA thresholds from leave-one-site-out predictor dissimilarity</t>
+    <t/>
   </si>
   <si>
     <t>Finite-value, row-count, support-class and manifest checks</t>
@@ -652,16 +652,16 @@
     <t>31 stations</t>
   </si>
   <si>
-    <t>Exact coordinates withheld in the public copy</t>
+    <t/>
   </si>
   <si>
     <t>Station ID and fold linkage checked</t>
   </si>
   <si>
-    <t>Included in the Supplementary workbook</t>
-  </si>
-  <si>
-    <t>No additional coordinate-precision restriction is applied</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Submission archive</t>
@@ -670,16 +670,16 @@
     <t>Versioned code and processed analysis package</t>
   </si>
   <si>
-    <t>Persistent identifier assigned at repository deposit</t>
+    <t/>
   </si>
   <si>
     <t>Checksum manifest and scripted inventory before submission</t>
   </si>
   <si>
-    <t>Code; processed response/covariates; folds; seeds; formulae; summaries; manifests</t>
-  </si>
-  <si>
-    <t>Repository link will appear in the journal Data Availability Statement</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Note. The journal requires a Data Availability Statement. The table defines the deposit contents without inventing a repository accession before the versioned archive is deposited.</t>
@@ -1645,8 +1645,10 @@
       <c r="C11" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>135</v>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>No new sampler for this composition: reuse completed daily HEQZ and hourly D1 posteriors.</t>
+        </is>
       </c>
       <c r="E11" s="7" t="s">
         <v>136</v>
@@ -1654,8 +1656,10 @@
       <c r="F11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>123</v>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Completed HEQZ and D1 components passed their MCMC checks; no incomplete direct host-by-hour fit contributed.</t>
+        </is>
       </c>
       <c r="H11" s="7" t="s">
         <v>138</v>
@@ -1981,66 +1985,54 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="58" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Monitoring coordinates</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>31 anonymised public station codes</t>
-        </is>
+      <c r="A14" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>209</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Station-level totals and fold membership in Table S1</t>
+          <t>De-identified station codes and fold assignments in Table S1</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Station-code, response-total and fold linkage checked before anonymisation</t>
-        </is>
+      <c r="D14" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Coordinates withheld; anonymised station summaries included</t>
+          <t>Exact coordinate records omitted from the public repository</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Exact recorder coordinates are restricted for site privacy and equipment security</t>
+          <t>Private identity mapping and precise positions are not distributed</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:6" ht="70" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Submission archive</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Versioned public code, aggregate verification data and supplementary assets</t>
-        </is>
+      <c r="A15" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Git history, release manifest and checksums</t>
+          <t>https://github.com/Fly-Carrot/urban-koel-acoustic-planning</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Contract scan, numerical tests and asset-level checksum validation</t>
-        </is>
+      <c r="D15" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Code; aggregate non-sensitive summaries; formula, seed and provenance registries; supplementary text, tables and figures</t>
+          <t>De-identified model inputs; folds; selected coefficient draws; code; processed summaries; manifests</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Raw audio, exact coordinates, station-level model-ready covariates, granular POIs and restricted model weights are excluded</t>
+          <t>Raw audio, precise coordinates and third-party source assets are not redistributed</t>
         </is>
       </c>
     </row>
